--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:39:21+00:00</t>
+    <t>2024-11-14T19:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:54:42+00:00</t>
+    <t>2024-11-29T17:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:43+00:00</t>
+    <t>2024-11-29T17:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/ext-radiation-level-score</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/ext-radiation-level-score</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:50+00:00</t>
+    <t>2024-12-05T15:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
     <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:44:48+00:00</t>
+    <t>2024-12-05T15:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:45:34+00:00</t>
+    <t>2024-12-05T15:45:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/ext-radiation-level-score</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/ext-radiation-level-score</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:45:53+00:00</t>
+    <t>2024-12-11T15:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
     <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:33:45+00:00</t>
+    <t>2024-12-11T16:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T16:17:48+00:00</t>
+    <t>2024-12-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:55:45+00:00</t>
+    <t>2024-12-23T16:34:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
